--- a/diseases/d054/1995-1999.xlsx
+++ b/diseases/d054/1995-1999.xlsx
@@ -8398,6 +8398,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8770,6 +8775,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9142,6 +9152,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9514,6 +9529,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9886,6 +9906,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10258,6 +10283,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10630,6 +10660,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11002,6 +11037,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11374,6 +11414,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11746,6 +11791,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12116,6 +12166,11 @@
       <c r="S57" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">

--- a/diseases/d054/1995-1999.xlsx
+++ b/diseases/d054/1995-1999.xlsx
@@ -8393,6 +8393,11 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8405,13 +8410,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8755,6 +8770,11 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8767,13 +8787,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9117,6 +9147,11 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9129,13 +9164,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9479,6 +9524,11 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9491,13 +9541,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9841,6 +9901,11 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9853,13 +9918,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10203,6 +10278,11 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10215,13 +10295,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10565,6 +10655,11 @@
       <c r="Q49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10577,13 +10672,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10927,6 +11032,11 @@
       <c r="Q51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10939,13 +11049,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11289,6 +11409,11 @@
       <c r="Q53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11301,13 +11426,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11651,6 +11786,11 @@
       <c r="Q55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11663,13 +11803,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12013,6 +12163,11 @@
       <c r="Q57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12025,12 +12180,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
